--- a/India_Semiconductor_Startup_Database.xlsx
+++ b/India_Semiconductor_Startup_Database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MihirAgarwal\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aekaadvisorsllp-my.sharepoint.com/personal/mihir_aekaadvisors_com/Documents/Desktop/Personal docs/IBR/Github/Semiconductor Market map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A30F1FD-A3CB-4DB4-BD9A-6996D36B1AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{1A30F1FD-A3CB-4DB4-BD9A-6996D36B1AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF104572-9139-43DB-889D-9048FF8F8423}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VC shortlist" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="Sources" sheetId="12" r:id="rId12"/>
     <sheet name="Method and definitions" sheetId="13" r:id="rId13"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -6417,7 +6417,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6432,6 +6432,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEDF4FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -6462,7 +6468,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6517,6 +6523,9 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6897,17 +6906,17 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TCompanyuniverse" displayName="TCompanyuniverse" ref="A5:H125" totalsRowShown="0" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TCompanyuniverse" displayName="TCompanyuniverse" ref="A5:H125" totalsRowShown="0" dataDxfId="8">
   <autoFilter ref="A5:H125" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Company" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Product / service category" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Ownership / eligibility boundary" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="State / India link" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Research coverage" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Official EDA roster no." dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Source IDs" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Company" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Product / service category" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Ownership / eligibility boundary" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="State / India link" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Research coverage" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Official EDA roster no." dataDxfId="1"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Source IDs" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7238,33 +7247,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="A1" s="22"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:10" ht="18">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="26" customHeight="1">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
